--- a/data/trans_bre/P68-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P68-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 7,99</t>
+          <t>-7,98; 7,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 1,86</t>
+          <t>-15,64; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,27</t>
+          <t>-13,0; 3,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 5,97</t>
+          <t>-6,92; 6,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 43,83</t>
+          <t>-34,58; 40,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 7,79</t>
+          <t>-48,35; 10,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 18,63</t>
+          <t>-48,6; 18,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 33,72</t>
+          <t>-27,68; 34,57</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 0,05</t>
+          <t>-12,23; 0,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 7,41</t>
+          <t>-5,97; 7,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 3,37</t>
+          <t>-10,27; 2,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 21,19</t>
+          <t>2,84; 21,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,57; 0,65</t>
+          <t>-43,79; 2,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 37,12</t>
+          <t>-23,33; 37,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 18,22</t>
+          <t>-37,33; 12,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 335,01</t>
+          <t>12,78; 377,0</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 2,44</t>
+          <t>-13,16; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 7,74</t>
+          <t>-7,65; 8,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 1,35</t>
+          <t>-14,07; 0,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 36,02</t>
+          <t>4,17; 38,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 9,89</t>
+          <t>-42,74; 6,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 35,74</t>
+          <t>-26,83; 36,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 5,11</t>
+          <t>-41,08; 2,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,7; 267,15</t>
+          <t>21,43; 268,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 3,92</t>
+          <t>-8,18; 3,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 8,37</t>
+          <t>-4,29; 8,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 4,27</t>
+          <t>-8,09; 5,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 6,04</t>
+          <t>-10,5; 6,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 17,88</t>
+          <t>-29,69; 17,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 50,51</t>
+          <t>-20,22; 51,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 22,26</t>
+          <t>-32,72; 25,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 29,58</t>
+          <t>-41,52; 35,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,33</t>
+          <t>-6,42; -0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 2,94</t>
+          <t>-4,03; 2,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -0,46</t>
+          <t>-7,25; -0,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,28</t>
+          <t>2,06; 14,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 1,28</t>
+          <t>-24,45; -0,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 12,92</t>
+          <t>-15,99; 13,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -1,23</t>
+          <t>-27,42; -1,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,36; 105,51</t>
+          <t>10,64; 109,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P68-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P68-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-1,08%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 7,59</t>
+          <t>-7,72; 8,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 2,8</t>
+          <t>-15,68; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 3,69</t>
+          <t>-12,19; 3,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 6,14</t>
+          <t>-5,04; 7,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 40,95</t>
+          <t>-32,97; 45,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 10,73</t>
+          <t>-47,98; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 18,64</t>
+          <t>-47,66; 19,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 34,57</t>
+          <t>-21,35; 42,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,04</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 0,31</t>
+          <t>-12,88; 0,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 7,48</t>
+          <t>-6,03; 7,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 2,65</t>
+          <t>-10,19; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 21,6</t>
+          <t>-2,04; 7,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 2,44</t>
+          <t>-44,24; 0,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 37,75</t>
+          <t>-24,25; 36,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 12,89</t>
+          <t>-38,5; 14,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 377,0</t>
+          <t>-9,21; 42,89</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 1,43</t>
+          <t>-12,18; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 8,19</t>
+          <t>-7,84; 8,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 0,45</t>
+          <t>-13,49; 0,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 38,49</t>
+          <t>-1,68; 10,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 6,31</t>
+          <t>-41,41; 13,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 36,3</t>
+          <t>-28,23; 39,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 2,47</t>
+          <t>-39,43; 2,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,43; 268,42</t>
+          <t>-8,15; 70,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,89</t>
+          <t>-7,51; 3,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,24</t>
+          <t>-3,67; 8,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 5,01</t>
+          <t>-7,74; 4,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 6,99</t>
+          <t>-2,07; 8,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 17,99</t>
+          <t>-27,61; 14,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 51,5</t>
+          <t>-16,59; 51,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 25,08</t>
+          <t>-30,67; 26,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,52; 35,68</t>
+          <t>-8,5; 45,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,09</t>
+          <t>-6,81; -0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,82</t>
+          <t>-3,79; 3,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,5</t>
+          <t>-7,7; -0,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 14,29</t>
+          <t>-0,01; 5,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -0,08</t>
+          <t>-26,05; -1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 13,2</t>
+          <t>-15,53; 15,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,42; -1,85</t>
+          <t>-28,19; 0,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 109,12</t>
+          <t>-0,02; 30,33</t>
         </is>
       </c>
     </row>
